--- a/DATA/ENGINEER SCHEDULES/ALLIED.xlsx
+++ b/DATA/ENGINEER SCHEDULES/ALLIED.xlsx
@@ -5,15 +5,16 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ericc\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\HHpro\DATA\ENGINEER SCHEDULES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7308D1C-4101-4D29-BD37-874834807D5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D59AA1D-962C-4376-9178-FB5D117BD712}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{C225A95A-C6F0-42F6-BF00-A93540BDA7B9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{C225A95A-C6F0-42F6-BF00-A93540BDA7B9}"/>
   </bookViews>
   <sheets>
     <sheet name="MULTI POSITION SPLIT" sheetId="1" r:id="rId1"/>
+    <sheet name="GAS SPLIT" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,10 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="32">
-  <si>
-    <t>SPLIT SYSTEM HEAT PUMP SCHEDULE</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="95">
   <si>
     <t>TAG</t>
   </si>
@@ -91,11 +89,6 @@
     <t>MOCP</t>
   </si>
   <si>
-    <t>DAIKIN HEAT
-PUMP MODEL
-NO.</t>
-  </si>
-  <si>
     <t>NOTES</t>
   </si>
   <si>
@@ -144,13 +137,229 @@
   <si>
     <t>HEAT PUMP
 HEAT</t>
+  </si>
+  <si>
+    <t>SPLIT SYSTEM GAS FURNACE SCHEDULE</t>
+  </si>
+  <si>
+    <t>UNIT TAG</t>
+  </si>
+  <si>
+    <t>TONNAGE</t>
+  </si>
+  <si>
+    <t>SERVING</t>
+  </si>
+  <si>
+    <t>DAIKIN FURNACE
+MODEL NO.</t>
+  </si>
+  <si>
+    <t>DAIKIN COOLING
+COIL MODEL NO.</t>
+  </si>
+  <si>
+    <t>TOTAL
+CFM</t>
+  </si>
+  <si>
+    <t>TOTAL
+OA</t>
+  </si>
+  <si>
+    <t>MBH
+INPUT</t>
+  </si>
+  <si>
+    <t>MBH
+OUTPUT</t>
+  </si>
+  <si>
+    <t>VOLTS</t>
+  </si>
+  <si>
+    <t>WEIGHT</t>
+  </si>
+  <si>
+    <t>DAIKIN COND UNIT
+MODEL NO. (CU)</t>
+  </si>
+  <si>
+    <t>ELECTRICAL DATA</t>
+  </si>
+  <si>
+    <t>ACCESSORIES</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8,9,10,11,12,13,14,15,16,17,18</t>
+  </si>
+  <si>
+    <t>COOLING CAPACITIES ARE RATED IN ACCORDANCE WITH ARI STANDARD 210/290 AT 95°F AMBIENT OUTDOOR AIR TEMP., 80°F DRY BULB, 67°F WET BULB ENTERING AIR TEMP., AND NOMINAL AIR QUANTITY LISTED.</t>
+  </si>
+  <si>
+    <t>AGA CERTIFIED UL LISTED AND LABELED.</t>
+  </si>
+  <si>
+    <t>PROVIDE WITH LOW AMBIENT KIT.</t>
+  </si>
+  <si>
+    <t>REFRIG. PIPING TO BE R-32, SIZED PER TOTAL INSTALLED EQUIVALENT LENGTH. LONG-LINE APPLICATION TO BE PROVIDED WHENEVER MFG. RECOMM. LENGTHS ARE EXCEEDED, INCL. LIQUID LINE SOLENOID VALVES, ACCUMULATOR, AND OTHER SPECIAL PRECAUTIONS PER MANUFACTURERS</t>
+  </si>
+  <si>
+    <t>RECOMMENDATIONS. MAX T.E.L. IS 100'</t>
+  </si>
+  <si>
+    <t>PROVIDE SINGLE POINT ELECTRICAL CONNECTION WITH FACTORY DISCONNECT KIT FOR BOTH INDOOR AND OUTDOOR UNIT.</t>
+  </si>
+  <si>
+    <t>PROVIDE MANUFACTURERS 7-DAY PROGRAMMABLE TOUCHSCREEN THERMOSTAT WITH AUTO-CHANGEOVER, CONTROL WIRING AND ASSOCIATED ACCESSORIES REQUIRED TO MEET SEQUENCE OF OPERATION. PROVIDE THERMOSTAT CLEAR LOCKING COVER.</t>
+  </si>
+  <si>
+    <t>CONDENSING UNIT TO BE INSTALLED LEVEL ON EQUIPMENT ROOF RAILS WITH VIBRATION ISOLATION.</t>
+  </si>
+  <si>
+    <t>CONDENSING UNIT TO BE INSTALLED LEVEL ON 4" UTILITY PAD</t>
+  </si>
+  <si>
+    <t>PROVIDE CONDENSATE OVERFLOW SENSOR IN DRAIN PAN TO DE-ENERGIZE UNIT SHOULD A CLOGGED CONDENSATE DRAIN CONDITION OCCUR.</t>
+  </si>
+  <si>
+    <t>PROVIDE A CONDENSATE OVERFLOW SENSOR IN DRAIN PAN. CONDENSATE PUMP SHALL BE WIRED TO DE-ENERGIZE UNIT SHOULD A CLOGGED CONDENSATE DRAIN CONDITION OCCUR.</t>
+  </si>
+  <si>
+    <t>PROVIDE TRANSFORMER AS REQUIRED FOR SUPPLY FAN.</t>
+  </si>
+  <si>
+    <t>PROVIDE DUCT SMOKE DETECTOR IN RETURN AIR DUCT.</t>
+  </si>
+  <si>
+    <t>PROVIDE HIGH-STATIC DRIVE AND ALTERNATE MOTOR.</t>
+  </si>
+  <si>
+    <t>PROVIDE VARIABLE SPEED SUPPLY FAN CONTROL FOR ENHANCED DEHUMIDIFICATION CAPABILITY</t>
+  </si>
+  <si>
+    <t>PROVIDE FACTORY INSTALLED NON-BLEED TXV, EVAPORATOR DEFROST CONTROLS AND AIR TIGHT CABINET CONSTRUCTION FOR INDOOR UNIT.</t>
+  </si>
+  <si>
+    <t>INDOOR UNIT SHALL BE PROVIDED WITH VIBRATION ISOLATION.</t>
+  </si>
+  <si>
+    <t>WARRANTY - 10 YR HEAT EXCHANGER / 5 YR COMPRESSOR / 3 YR CONTROLLER.</t>
+  </si>
+  <si>
+    <t>PROVIDE MIXING BOX.</t>
+  </si>
+  <si>
+    <t>PROVIDE HAIL GUARDS - FACTORY SUPPLIED, FIELD INSTALLED FOR OUTDOOR UNIT.</t>
+  </si>
+  <si>
+    <t>PROVIDE CORROSION PROTECTION.</t>
+  </si>
+  <si>
+    <t>VARIABLE SPEED SCROLL COMPRESSOR.</t>
+  </si>
+  <si>
+    <t>2 STAGE SCROLL COMPRESSOR</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">     </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>NOTES &amp; ACCESSORIES:</t>
+    </r>
+  </si>
+  <si>
+    <t>SPLIT SYSTEM SCHEDULE</t>
+  </si>
+  <si>
+    <t>AHU-1</t>
+  </si>
+  <si>
+    <t>AHU-2</t>
+  </si>
+  <si>
+    <t>AMST42CU1300</t>
+  </si>
+  <si>
+    <t>AMST60DU1300</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>14.5/12.0 (SEER2/EER2)</t>
+  </si>
+  <si>
+    <t>16.0/12.0 (SEER2/EER2)</t>
+  </si>
+  <si>
+    <t>208/1</t>
+  </si>
+  <si>
+    <t>CU-1</t>
+  </si>
+  <si>
+    <t>CU-2</t>
+  </si>
+  <si>
+    <t>DAIKIN CONDENSING
+UNIT MODEL NO.</t>
+  </si>
+  <si>
+    <t>DC4SEA4210</t>
+  </si>
+  <si>
+    <t>DH5SEA6010</t>
+  </si>
+  <si>
+    <t>1,2,3,4,5,6,7,8</t>
+  </si>
+  <si>
+    <t>DR80TN0803BN</t>
+  </si>
+  <si>
+    <t>DR80TN1005CN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHPTA3026B3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHPTA4830C3 </t>
+  </si>
+  <si>
+    <t>115/1</t>
+  </si>
+  <si>
+    <t>DC4SEA3010</t>
+  </si>
+  <si>
+    <t>DC4SEA4810</t>
+  </si>
+  <si>
+    <t>15.2 / 12</t>
+  </si>
+  <si>
+    <t>14.5 / 11.7</t>
+  </si>
+  <si>
+    <t>EFFICIENCY
+(SEER2 / EER2)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -170,6 +379,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -179,7 +395,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -282,11 +498,74 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -312,12 +591,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -335,6 +608,30 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -684,157 +981,247 @@
     <col min="10" max="10" width="4.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="21.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="14" max="19" width="9.140625" style="1"/>
-    <col min="20" max="20" width="13" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="20" max="20" width="19" style="1" customWidth="1"/>
+    <col min="21" max="23" width="9.140625" style="1"/>
+    <col min="24" max="24" width="14.140625" style="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="3:24" ht="23.25" x14ac:dyDescent="0.25">
-      <c r="C1" s="16" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
-      <c r="M1" s="16"/>
-      <c r="N1" s="16"/>
-      <c r="O1" s="16"/>
-      <c r="P1" s="16"/>
-      <c r="Q1" s="16"/>
-      <c r="R1" s="16"/>
-      <c r="S1" s="16"/>
-      <c r="T1" s="16"/>
-      <c r="U1" s="16"/>
-      <c r="V1" s="16"/>
-      <c r="W1" s="16"/>
-      <c r="X1" s="16"/>
+      <c r="C1" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
     </row>
     <row r="2" spans="3:24" ht="45" x14ac:dyDescent="0.25">
       <c r="C2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="T2" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="U2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="X2" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3.5</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="2">
+        <v>1390</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="2">
+        <v>0.75</v>
+      </c>
+      <c r="J3" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="2">
+        <v>40</v>
+      </c>
+      <c r="L3" s="2">
+        <v>30.8</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q3" s="2">
+        <v>5.9</v>
+      </c>
+      <c r="R3" s="2">
+        <v>15</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V3" s="2">
+        <v>19</v>
+      </c>
+      <c r="W3" s="2">
         <v>30</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="X3" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2">
+        <v>5</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>60.8</v>
+      </c>
+      <c r="L4" s="2">
+        <v>48.32</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N4" s="2">
+        <v>60.4</v>
+      </c>
+      <c r="O4" s="2">
         <v>3</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="U2" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="V2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="W2" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="X2" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="3" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-    </row>
-    <row r="4" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
+      <c r="P4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>22</v>
+      </c>
+      <c r="R4" s="2">
+        <v>25</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="V4" s="2">
+        <v>38.799999999999997</v>
+      </c>
+      <c r="W4" s="2">
+        <v>60</v>
+      </c>
+      <c r="X4" s="2" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="5" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C5" s="5" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -862,496 +1249,154 @@
       <c r="C6" s="8">
         <v>1</v>
       </c>
-      <c r="D6" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="10"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="10"/>
-      <c r="K6" s="10"/>
-      <c r="L6" s="10"/>
-      <c r="M6" s="10"/>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
-      <c r="Q6" s="10"/>
-      <c r="R6" s="10"/>
-      <c r="S6" s="10"/>
-      <c r="T6" s="10"/>
-      <c r="U6" s="10"/>
-      <c r="V6" s="10"/>
-      <c r="W6" s="10"/>
-      <c r="X6" s="11"/>
+      <c r="D6" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="X6" s="9"/>
     </row>
     <row r="7" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C7" s="8"/>
-      <c r="D7" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
-      <c r="G7" s="10"/>
-      <c r="H7" s="10"/>
-      <c r="I7" s="10"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="10"/>
-      <c r="M7" s="10"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
-      <c r="Q7" s="10"/>
-      <c r="R7" s="10"/>
-      <c r="S7" s="10"/>
-      <c r="T7" s="10"/>
-      <c r="U7" s="10"/>
-      <c r="V7" s="10"/>
-      <c r="W7" s="10"/>
-      <c r="X7" s="11"/>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="X7" s="9"/>
     </row>
     <row r="8" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C8" s="8"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
-      <c r="G8" s="10"/>
-      <c r="H8" s="10"/>
-      <c r="I8" s="10"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10"/>
-      <c r="L8" s="10"/>
-      <c r="M8" s="10"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="10"/>
-      <c r="P8" s="10"/>
-      <c r="Q8" s="10"/>
-      <c r="R8" s="10"/>
-      <c r="S8" s="10"/>
-      <c r="T8" s="10"/>
-      <c r="U8" s="10"/>
-      <c r="V8" s="10"/>
-      <c r="W8" s="10"/>
-      <c r="X8" s="11"/>
+      <c r="D8" s="4"/>
+      <c r="X8" s="9"/>
     </row>
     <row r="9" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C9" s="8">
         <v>2</v>
       </c>
-      <c r="D9" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
-      <c r="G9" s="10"/>
-      <c r="H9" s="10"/>
-      <c r="I9" s="10"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10"/>
-      <c r="L9" s="10"/>
-      <c r="M9" s="10"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="10"/>
-      <c r="P9" s="10"/>
-      <c r="Q9" s="10"/>
-      <c r="R9" s="10"/>
-      <c r="S9" s="10"/>
-      <c r="T9" s="10"/>
-      <c r="U9" s="10"/>
-      <c r="V9" s="10"/>
-      <c r="W9" s="10"/>
-      <c r="X9" s="11"/>
+      <c r="D9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="X9" s="9"/>
     </row>
     <row r="10" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C10" s="8"/>
-      <c r="D10" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
-      <c r="G10" s="10"/>
-      <c r="H10" s="10"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10"/>
-      <c r="L10" s="10"/>
-      <c r="M10" s="10"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="10"/>
-      <c r="P10" s="10"/>
-      <c r="Q10" s="10"/>
-      <c r="R10" s="10"/>
-      <c r="S10" s="10"/>
-      <c r="T10" s="10"/>
-      <c r="U10" s="10"/>
-      <c r="V10" s="10"/>
-      <c r="W10" s="10"/>
-      <c r="X10" s="11"/>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="X10" s="9"/>
     </row>
     <row r="11" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C11" s="8"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="10"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="10"/>
-      <c r="M11" s="10"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="10"/>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="10"/>
-      <c r="S11" s="10"/>
-      <c r="T11" s="10"/>
-      <c r="U11" s="10"/>
-      <c r="V11" s="10"/>
-      <c r="W11" s="10"/>
-      <c r="X11" s="11"/>
+      <c r="D11" s="4"/>
+      <c r="X11" s="9"/>
     </row>
     <row r="12" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C12" s="8">
         <v>3</v>
       </c>
-      <c r="D12" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-      <c r="K12" s="10"/>
-      <c r="L12" s="10"/>
-      <c r="M12" s="10"/>
-      <c r="N12" s="10"/>
-      <c r="O12" s="10"/>
-      <c r="P12" s="10"/>
-      <c r="Q12" s="10"/>
-      <c r="R12" s="10"/>
-      <c r="S12" s="10"/>
-      <c r="T12" s="10"/>
-      <c r="U12" s="10"/>
-      <c r="V12" s="10"/>
-      <c r="W12" s="10"/>
-      <c r="X12" s="11"/>
+      <c r="D12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="X12" s="9"/>
     </row>
     <row r="13" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C13" s="8"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="10"/>
-      <c r="G13" s="10"/>
-      <c r="H13" s="10"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="10"/>
-      <c r="K13" s="10"/>
-      <c r="L13" s="10"/>
-      <c r="M13" s="10"/>
-      <c r="N13" s="10"/>
-      <c r="O13" s="10"/>
-      <c r="P13" s="10"/>
-      <c r="Q13" s="10"/>
-      <c r="R13" s="10"/>
-      <c r="S13" s="10"/>
-      <c r="T13" s="10"/>
-      <c r="U13" s="10"/>
-      <c r="V13" s="10"/>
-      <c r="W13" s="10"/>
-      <c r="X13" s="11"/>
+      <c r="D13" s="4"/>
+      <c r="X13" s="9"/>
     </row>
     <row r="14" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C14" s="8">
         <v>4</v>
       </c>
-      <c r="D14" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="10"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="10"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="10"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="10"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="10"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="10"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="10"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="10"/>
-      <c r="U14" s="10"/>
-      <c r="V14" s="10"/>
-      <c r="W14" s="10"/>
-      <c r="X14" s="11"/>
+      <c r="D14" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="X14" s="9"/>
     </row>
     <row r="15" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C15" s="8"/>
-      <c r="D15" s="9"/>
-      <c r="E15" s="10"/>
-      <c r="F15" s="10"/>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="10"/>
-      <c r="M15" s="10"/>
-      <c r="N15" s="10"/>
-      <c r="O15" s="10"/>
-      <c r="P15" s="10"/>
-      <c r="Q15" s="10"/>
-      <c r="R15" s="10"/>
-      <c r="S15" s="10"/>
-      <c r="T15" s="10"/>
-      <c r="U15" s="10"/>
-      <c r="V15" s="10"/>
-      <c r="W15" s="10"/>
-      <c r="X15" s="11"/>
+      <c r="D15" s="4"/>
+      <c r="X15" s="9"/>
     </row>
     <row r="16" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C16" s="8">
         <v>5</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="E16" s="10"/>
-      <c r="F16" s="10"/>
-      <c r="G16" s="10"/>
-      <c r="H16" s="10"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="10"/>
-      <c r="K16" s="10"/>
-      <c r="L16" s="10"/>
-      <c r="M16" s="10"/>
-      <c r="N16" s="10"/>
-      <c r="O16" s="10"/>
-      <c r="P16" s="10"/>
-      <c r="Q16" s="10"/>
-      <c r="R16" s="10"/>
-      <c r="S16" s="10"/>
-      <c r="T16" s="10"/>
-      <c r="U16" s="10"/>
-      <c r="V16" s="10"/>
-      <c r="W16" s="10"/>
-      <c r="X16" s="11"/>
+      <c r="D16" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="X16" s="9"/>
     </row>
     <row r="17" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="8"/>
-      <c r="D17" s="9"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-      <c r="K17" s="10"/>
-      <c r="L17" s="10"/>
-      <c r="M17" s="10"/>
-      <c r="N17" s="10"/>
-      <c r="O17" s="10"/>
-      <c r="P17" s="10"/>
-      <c r="Q17" s="10"/>
-      <c r="R17" s="10"/>
-      <c r="S17" s="10"/>
-      <c r="T17" s="10"/>
-      <c r="U17" s="10"/>
-      <c r="V17" s="10"/>
-      <c r="W17" s="10"/>
-      <c r="X17" s="11"/>
+      <c r="D17" s="4"/>
+      <c r="X17" s="9"/>
     </row>
     <row r="18" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C18" s="8">
         <v>6</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-      <c r="K18" s="10"/>
-      <c r="L18" s="10"/>
-      <c r="M18" s="10"/>
-      <c r="N18" s="10"/>
-      <c r="O18" s="10"/>
-      <c r="P18" s="10"/>
-      <c r="Q18" s="10"/>
-      <c r="R18" s="10"/>
-      <c r="S18" s="10"/>
-      <c r="T18" s="10"/>
-      <c r="U18" s="10"/>
-      <c r="V18" s="10"/>
-      <c r="W18" s="10"/>
-      <c r="X18" s="11"/>
+      <c r="D18" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="X18" s="9"/>
     </row>
     <row r="19" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C19" s="8"/>
-      <c r="D19" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-      <c r="K19" s="10"/>
-      <c r="L19" s="10"/>
-      <c r="M19" s="10"/>
-      <c r="N19" s="10"/>
-      <c r="O19" s="10"/>
-      <c r="P19" s="10"/>
-      <c r="Q19" s="10"/>
-      <c r="R19" s="10"/>
-      <c r="S19" s="10"/>
-      <c r="T19" s="10"/>
-      <c r="U19" s="10"/>
-      <c r="V19" s="10"/>
-      <c r="W19" s="10"/>
-      <c r="X19" s="11"/>
+      <c r="D19" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="X19" s="9"/>
     </row>
     <row r="20" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="8"/>
-      <c r="D20" s="9"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-      <c r="K20" s="10"/>
-      <c r="L20" s="10"/>
-      <c r="M20" s="10"/>
-      <c r="N20" s="10"/>
-      <c r="O20" s="10"/>
-      <c r="P20" s="10"/>
-      <c r="Q20" s="10"/>
-      <c r="R20" s="10"/>
-      <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="10"/>
-      <c r="V20" s="10"/>
-      <c r="W20" s="10"/>
-      <c r="X20" s="11"/>
+      <c r="D20" s="4"/>
+      <c r="X20" s="9"/>
     </row>
     <row r="21" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C21" s="8">
         <v>7</v>
       </c>
-      <c r="D21" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
-      <c r="N21" s="10"/>
-      <c r="O21" s="10"/>
-      <c r="P21" s="10"/>
-      <c r="Q21" s="10"/>
-      <c r="R21" s="10"/>
-      <c r="S21" s="10"/>
-      <c r="T21" s="10"/>
-      <c r="U21" s="10"/>
-      <c r="V21" s="10"/>
-      <c r="W21" s="10"/>
-      <c r="X21" s="11"/>
+      <c r="D21" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="X21" s="9"/>
     </row>
     <row r="22" spans="3:24" ht="6.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="8"/>
-      <c r="D22" s="9"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-      <c r="K22" s="10"/>
-      <c r="L22" s="10"/>
-      <c r="M22" s="10"/>
-      <c r="N22" s="10"/>
-      <c r="O22" s="10"/>
-      <c r="P22" s="10"/>
-      <c r="Q22" s="10"/>
-      <c r="R22" s="10"/>
-      <c r="S22" s="10"/>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="10"/>
-      <c r="W22" s="10"/>
-      <c r="X22" s="11"/>
+      <c r="D22" s="4"/>
+      <c r="X22" s="9"/>
     </row>
     <row r="23" spans="3:24" x14ac:dyDescent="0.25">
       <c r="C23" s="8">
         <v>8</v>
       </c>
-      <c r="D23" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-      <c r="K23" s="10"/>
-      <c r="L23" s="10"/>
-      <c r="M23" s="10"/>
-      <c r="N23" s="10"/>
-      <c r="O23" s="10"/>
-      <c r="P23" s="10"/>
-      <c r="Q23" s="10"/>
-      <c r="R23" s="10"/>
-      <c r="S23" s="10"/>
-      <c r="T23" s="10"/>
-      <c r="U23" s="10"/>
-      <c r="V23" s="10"/>
-      <c r="W23" s="10"/>
-      <c r="X23" s="11"/>
+      <c r="D23" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X23" s="9"/>
     </row>
     <row r="24" spans="3:24" x14ac:dyDescent="0.25">
-      <c r="C24" s="12"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
-      <c r="Q24" s="14"/>
-      <c r="R24" s="14"/>
-      <c r="S24" s="14"/>
-      <c r="T24" s="14"/>
-      <c r="U24" s="14"/>
-      <c r="V24" s="14"/>
-      <c r="W24" s="14"/>
-      <c r="X24" s="15" t="s">
-        <v>29</v>
+      <c r="C24" s="10"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="25" spans="3:24" x14ac:dyDescent="0.25">
@@ -1376,4 +1421,667 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF6539A-3E62-4B6F-82AA-1F326DD94527}">
+  <dimension ref="C1:AA36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="9.140625" style="1"/>
+    <col min="3" max="3" width="15.140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="21.42578125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="6.85546875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.5703125" style="1" customWidth="1"/>
+    <col min="13" max="14" width="9.5703125" style="1" customWidth="1"/>
+    <col min="15" max="19" width="9.140625" style="1"/>
+    <col min="20" max="20" width="19.7109375" style="1" customWidth="1"/>
+    <col min="21" max="21" width="13" style="1" customWidth="1"/>
+    <col min="22" max="22" width="15.7109375" style="1" customWidth="1"/>
+    <col min="23" max="24" width="10.85546875" style="1" customWidth="1"/>
+    <col min="25" max="26" width="9.140625" style="1"/>
+    <col min="27" max="27" width="44.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="3:27" ht="23.25" x14ac:dyDescent="0.25">
+      <c r="C1" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+      <c r="L1" s="14"/>
+      <c r="M1" s="14"/>
+      <c r="N1" s="14"/>
+      <c r="O1" s="14"/>
+      <c r="P1" s="14"/>
+      <c r="Q1" s="14"/>
+      <c r="R1" s="14"/>
+      <c r="S1" s="14"/>
+      <c r="T1" s="14"/>
+      <c r="U1" s="14"/>
+      <c r="V1" s="14"/>
+      <c r="W1" s="14"/>
+      <c r="X1" s="14"/>
+      <c r="Y1" s="14"/>
+      <c r="Z1" s="14"/>
+      <c r="AA1" s="14"/>
+    </row>
+    <row r="2" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="N2" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="O2" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="S2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="T2" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="U2" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="V2" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="W2" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="X2" s="19"/>
+      <c r="Y2" s="20"/>
+      <c r="Z2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="AA2" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
+      <c r="N3" s="16"/>
+      <c r="O3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="R3" s="16"/>
+      <c r="S3" s="16"/>
+      <c r="T3" s="16"/>
+      <c r="U3" s="16"/>
+      <c r="V3" s="16"/>
+      <c r="W3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+    </row>
+    <row r="4" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>910</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="K4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L4" s="2">
+        <v>28.4</v>
+      </c>
+      <c r="M4" s="2">
+        <v>80</v>
+      </c>
+      <c r="N4" s="2">
+        <v>64</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P4" s="2">
+        <v>8.6999999999999993</v>
+      </c>
+      <c r="Q4" s="2">
+        <v>15</v>
+      </c>
+      <c r="R4" s="2">
+        <v>176</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="U4" s="2">
+        <v>2.5</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X4" s="2">
+        <v>15.4</v>
+      </c>
+      <c r="Y4" s="2">
+        <v>25</v>
+      </c>
+      <c r="Z4" s="2">
+        <v>174</v>
+      </c>
+      <c r="AA4" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="5" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C5" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F5" s="2">
+        <v>4</v>
+      </c>
+      <c r="G5" s="2">
+        <v>1330</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="L5" s="2">
+        <v>45.5</v>
+      </c>
+      <c r="M5" s="2">
+        <v>100</v>
+      </c>
+      <c r="N5" s="2">
+        <v>80</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="P5" s="2">
+        <v>15.32</v>
+      </c>
+      <c r="Q5" s="2">
+        <v>20</v>
+      </c>
+      <c r="R5" s="2">
+        <v>206</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="U5" s="2">
+        <v>4</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="X5" s="2">
+        <v>25.19</v>
+      </c>
+      <c r="Y5" s="2">
+        <v>40</v>
+      </c>
+      <c r="Z5" s="2">
+        <v>241</v>
+      </c>
+      <c r="AA5" s="2" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C6" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="22"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
+      <c r="AA6" s="7"/>
+    </row>
+    <row r="7" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C7" s="8">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="AA7" s="9"/>
+    </row>
+    <row r="8" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C8" s="8">
+        <v>2</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" s="4"/>
+      <c r="AA8" s="9"/>
+    </row>
+    <row r="9" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C9" s="8">
+        <v>3</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="4"/>
+      <c r="AA9" s="9"/>
+    </row>
+    <row r="10" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C10" s="8">
+        <v>4</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="4"/>
+      <c r="AA10" s="9"/>
+    </row>
+    <row r="11" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C11" s="8"/>
+      <c r="D11" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="4"/>
+      <c r="AA11" s="9"/>
+    </row>
+    <row r="12" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C12" s="8">
+        <v>5</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="4"/>
+      <c r="AA12" s="9"/>
+    </row>
+    <row r="13" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C13" s="8">
+        <v>6</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="4"/>
+      <c r="AA13" s="9"/>
+    </row>
+    <row r="14" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C14" s="8">
+        <v>7</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E14" s="4"/>
+      <c r="AA14" s="9"/>
+    </row>
+    <row r="15" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C15" s="8">
+        <v>8</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="4"/>
+      <c r="AA15" s="9"/>
+    </row>
+    <row r="16" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C16" s="8">
+        <v>9</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="4"/>
+      <c r="AA16" s="9"/>
+    </row>
+    <row r="17" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C17" s="8">
+        <v>10</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E17" s="4"/>
+      <c r="AA17" s="9"/>
+    </row>
+    <row r="18" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C18" s="8">
+        <v>11</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="4"/>
+      <c r="AA18" s="9"/>
+    </row>
+    <row r="19" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="8">
+        <v>12</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E19" s="4"/>
+      <c r="AA19" s="9"/>
+    </row>
+    <row r="20" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="8">
+        <v>13</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="AA20" s="9"/>
+    </row>
+    <row r="21" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C21" s="8">
+        <v>14</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" s="4"/>
+      <c r="AA21" s="9"/>
+    </row>
+    <row r="22" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C22" s="8">
+        <v>15</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="4"/>
+      <c r="AA22" s="9"/>
+    </row>
+    <row r="23" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="8">
+        <v>16</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E23" s="4"/>
+      <c r="AA23" s="9"/>
+    </row>
+    <row r="24" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C24" s="8">
+        <v>17</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="4"/>
+      <c r="AA24" s="9"/>
+    </row>
+    <row r="25" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C25" s="8">
+        <v>18</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E25" s="4"/>
+      <c r="AA25" s="9"/>
+    </row>
+    <row r="26" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="8">
+        <v>19</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E26" s="4"/>
+      <c r="AA26" s="9"/>
+    </row>
+    <row r="27" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C27" s="8">
+        <v>20</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="4"/>
+      <c r="AA27" s="9"/>
+    </row>
+    <row r="28" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C28" s="8">
+        <v>21</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E28" s="4"/>
+      <c r="AA28" s="9"/>
+    </row>
+    <row r="29" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C29" s="8">
+        <v>22</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E29" s="4"/>
+      <c r="AA29" s="9"/>
+    </row>
+    <row r="30" spans="3:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C30" s="8">
+        <v>23</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="E30" s="4"/>
+      <c r="AA30" s="9"/>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="C31" s="10"/>
+      <c r="D31" s="11"/>
+      <c r="E31" s="11"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
+      <c r="AA31" s="13" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.25">
+      <c r="D32" s="4"/>
+      <c r="E32" s="4"/>
+    </row>
+    <row r="33" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D33" s="4"/>
+      <c r="E33" s="4"/>
+    </row>
+    <row r="34" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+    </row>
+    <row r="35" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+    </row>
+    <row r="36" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+    </row>
+  </sheetData>
+  <mergeCells count="23">
+    <mergeCell ref="V2:V3"/>
+    <mergeCell ref="Z2:Z3"/>
+    <mergeCell ref="AA2:AA3"/>
+    <mergeCell ref="W2:Y2"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="R2:R3"/>
+    <mergeCell ref="S2:S3"/>
+    <mergeCell ref="T2:T3"/>
+    <mergeCell ref="U2:U3"/>
+    <mergeCell ref="K2:K3"/>
+    <mergeCell ref="L2:L3"/>
+    <mergeCell ref="M2:M3"/>
+    <mergeCell ref="N2:N3"/>
+    <mergeCell ref="C1:AA1"/>
+    <mergeCell ref="O2:Q2"/>
+    <mergeCell ref="C2:C3"/>
+    <mergeCell ref="D2:D3"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="H2:H3"/>
+    <mergeCell ref="I2:I3"/>
+    <mergeCell ref="J2:J3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>